--- a/outputs/model_comparison_result.xlsx
+++ b/outputs/model_comparison_result.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="model_comparison" sheetId="1" r:id="rId1"/>
@@ -15,20 +15,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>Model</t>
   </si>
   <si>
-    <t>Random</t>
-  </si>
-  <si>
-    <t>Time-Based</t>
-  </si>
-  <si>
-    <t>Walk-Forward</t>
-  </si>
-  <si>
     <t>Linear Regression</t>
   </si>
   <si>
@@ -60,6 +51,21 @@
   </si>
   <si>
     <t>Average RMSE</t>
+  </si>
+  <si>
+    <t>Random RMSE</t>
+  </si>
+  <si>
+    <t>Time RMSE</t>
+  </si>
+  <si>
+    <t>Walk RMSE</t>
+  </si>
+  <si>
+    <t>XGBoost</t>
+  </si>
+  <si>
+    <t>MLP</t>
   </si>
 </sst>
 </file>
@@ -421,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" customWidth="1"/>
@@ -435,18 +441,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
       </c>
       <c r="B2" s="2">
         <v>8.35</v>
@@ -458,9 +464,9 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2">
         <v>12.77</v>
@@ -474,7 +480,7 @@
     </row>
     <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2">
         <v>9.1300000000000008</v>
@@ -484,6 +490,34 @@
       </c>
       <c r="D4" s="2">
         <v>48.65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2">
+        <v>23.82</v>
+      </c>
+      <c r="D5" s="2">
+        <v>51.97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="C6" s="2">
+        <v>30.58</v>
+      </c>
+      <c r="D6" s="2">
+        <v>26.1</v>
       </c>
     </row>
   </sheetData>
@@ -505,27 +539,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2">
         <v>3.05</v>
@@ -537,12 +571,12 @@
         <v>13.47</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2">
         <v>7.51</v>
@@ -554,12 +588,12 @@
         <v>133.31</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2">
         <v>9.76</v>
@@ -571,12 +605,12 @@
         <v>36.94</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2">
         <v>14.22</v>
@@ -588,12 +622,12 @@
         <v>48.92</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2">
         <v>8.91</v>
@@ -610,12 +644,12 @@
         <v>0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B12" s="2">
         <v>8.69</v>
@@ -623,7 +657,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B13" s="2">
         <v>48.65</v>
@@ -631,7 +665,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B14" s="2">
         <v>53.94</v>

--- a/outputs/model_comparison_result.xlsx
+++ b/outputs/model_comparison_result.xlsx
@@ -4,18 +4,20 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="model_comparison" sheetId="1" r:id="rId1"/>
-    <sheet name="fold_analysis_table" sheetId="2" r:id="rId2"/>
+    <sheet name="master_table" sheetId="3" r:id="rId2"/>
+    <sheet name="fold_analysis_table" sheetId="2" r:id="rId3"/>
+    <sheet name="Apple" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="29">
   <si>
     <t>Model</t>
   </si>
@@ -66,13 +68,49 @@
   </si>
   <si>
     <t>MLP</t>
+  </si>
+  <si>
+    <t>LSTM Version</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>RMSE</t>
+  </si>
+  <si>
+    <t>R²</t>
+  </si>
+  <si>
+    <t>Raw OHLCV</t>
+  </si>
+  <si>
+    <t>Engineered Features</t>
+  </si>
+  <si>
+    <t>Best RMSE</t>
+  </si>
+  <si>
+    <t>Δ Random→Walk</t>
+  </si>
+  <si>
+    <t>...</t>
+  </si>
+  <si>
+    <t>Raw LSTM</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>All Engineered Features LSTM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,6 +125,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFD6DEEB"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -109,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -123,11 +167,116 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="19">
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -138,6 +287,49 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="E9:H12" totalsRowShown="0" headerRowDxfId="18">
+  <autoFilter ref="E9:H12"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="LSTM Version" dataDxfId="17"/>
+    <tableColumn id="2" name="Units" dataDxfId="16"/>
+    <tableColumn id="3" name="RMSE"/>
+    <tableColumn id="4" name="R²"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F8" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:F8"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Model" dataDxfId="13"/>
+    <tableColumn id="2" name="Random RMSE" dataDxfId="12"/>
+    <tableColumn id="3" name="Time RMSE" dataDxfId="11"/>
+    <tableColumn id="4" name="Walk RMSE" dataDxfId="10"/>
+    <tableColumn id="5" name="Best RMSE" dataDxfId="9"/>
+    <tableColumn id="6" name="Δ Random→Walk" dataDxfId="8"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table15" displayName="Table15" ref="A1:F8" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="A1:F8"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Model" dataDxfId="5"/>
+    <tableColumn id="2" name="Random RMSE" dataDxfId="4"/>
+    <tableColumn id="3" name="Time RMSE" dataDxfId="3"/>
+    <tableColumn id="4" name="Walk RMSE" dataDxfId="2"/>
+    <tableColumn id="5" name="Best RMSE" dataDxfId="1"/>
+    <tableColumn id="6" name="Δ Random→Walk" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -427,16 +619,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" customWidth="1"/>
     <col min="3" max="3" width="13.109375" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" customWidth="1"/>
+    <col min="6" max="6" width="16.5546875" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -450,7 +646,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -464,7 +660,7 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -478,7 +674,7 @@
         <v>53.94</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -492,7 +688,7 @@
         <v>48.65</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -506,7 +702,7 @@
         <v>51.97</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
@@ -520,12 +716,251 @@
         <v>26.1</v>
       </c>
     </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="2">
+        <v>50</v>
+      </c>
+      <c r="G10" s="2">
+        <v>19.940000000000001</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.95089999999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="2">
+        <v>50</v>
+      </c>
+      <c r="G11" s="2">
+        <v>41.36</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.78859999999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="2">
+        <v>100</v>
+      </c>
+      <c r="G12" s="3">
+        <v>29.4</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.89319999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.21875" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>8.6024774970882891</v>
+      </c>
+      <c r="C2" s="2">
+        <v>12.8340994729757</v>
+      </c>
+      <c r="D2" s="2">
+        <v>10.260938786791</v>
+      </c>
+      <c r="E2" s="2">
+        <v>8.6024774970882891</v>
+      </c>
+      <c r="F2" s="2">
+        <f>ABS(B2-D2)</f>
+        <v>1.6584612897027107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>12.767838034677199</v>
+      </c>
+      <c r="C3" s="2">
+        <v>29.230835798083699</v>
+      </c>
+      <c r="D3" s="2">
+        <v>53.940100130441003</v>
+      </c>
+      <c r="E3" s="2">
+        <v>12.767838034677199</v>
+      </c>
+      <c r="F3" s="2">
+        <f t="shared" ref="F3:F6" si="0">ABS(B3-D3)</f>
+        <v>41.172262095763806</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>9.1270676133805697</v>
+      </c>
+      <c r="C4" s="2">
+        <v>16.8106414161781</v>
+      </c>
+      <c r="D4" s="2">
+        <v>48.6558650628793</v>
+      </c>
+      <c r="E4" s="2">
+        <v>9.1270676133805697</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" si="0"/>
+        <v>39.528797449498732</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2">
+        <v>9.4238145778730598</v>
+      </c>
+      <c r="C5" s="2">
+        <v>23.066939177986001</v>
+      </c>
+      <c r="D5" s="2">
+        <v>51.9654495245303</v>
+      </c>
+      <c r="E5" s="2">
+        <v>9.4238145778730598</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="0"/>
+        <v>42.54163494665724</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2">
+        <v>9.1194110478356905</v>
+      </c>
+      <c r="C6" s="2">
+        <v>30.5753313206352</v>
+      </c>
+      <c r="D6" s="2">
+        <v>26.099956053911399</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="0"/>
+        <v>16.980545006075708</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="2">
+        <v>19.940000000000001</v>
+      </c>
+      <c r="D7" s="6">
+        <v>57.832911911225601</v>
+      </c>
+      <c r="E7" s="2">
+        <v>19.940000000000001</v>
+      </c>
+      <c r="F7" s="6">
+        <v>57.832911911225601</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8">
+        <v>29.3986012905469</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D14" s="5"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D16" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -674,4 +1109,237 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6">
+        <v>4.4495586506269298</v>
+      </c>
+      <c r="C2" s="6">
+        <v>7.3314479275857503</v>
+      </c>
+      <c r="D2" s="2">
+        <v>10.260938786791</v>
+      </c>
+      <c r="E2" s="6">
+        <v>4.4495586506269298</v>
+      </c>
+      <c r="F2" s="2">
+        <f>ABS(B2-D2)</f>
+        <v>5.81138013616407</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6">
+        <v>3.3807335861675001</v>
+      </c>
+      <c r="C3" s="6">
+        <v>35.8586877169991</v>
+      </c>
+      <c r="D3" s="2">
+        <v>53.940100130441003</v>
+      </c>
+      <c r="E3" s="6">
+        <v>3.3807335861675001</v>
+      </c>
+      <c r="F3" s="2">
+        <f t="shared" ref="F3:F6" si="0">ABS(B3-D3)</f>
+        <v>50.559366544273502</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6">
+        <v>2.71393967817533</v>
+      </c>
+      <c r="C4" s="6">
+        <v>37.102660473070898</v>
+      </c>
+      <c r="D4" s="2">
+        <v>48.6558650628793</v>
+      </c>
+      <c r="E4" s="6">
+        <v>2.71393967817533</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" si="0"/>
+        <v>45.941925384703971</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2">
+        <v>9.4238145778730598</v>
+      </c>
+      <c r="C5" s="2">
+        <v>23.066939177986001</v>
+      </c>
+      <c r="D5" s="2">
+        <v>51.9654495245303</v>
+      </c>
+      <c r="E5" s="2">
+        <v>9.4238145778730598</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="0"/>
+        <v>42.54163494665724</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2">
+        <v>9.1194110478356905</v>
+      </c>
+      <c r="C6" s="2">
+        <v>30.5753313206352</v>
+      </c>
+      <c r="D6" s="2">
+        <v>26.099956053911399</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="0"/>
+        <v>16.980545006075708</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="2">
+        <v>19.940000000000001</v>
+      </c>
+      <c r="D7" s="6">
+        <v>57.832911911225601</v>
+      </c>
+      <c r="E7" s="2">
+        <v>19.940000000000001</v>
+      </c>
+      <c r="F7" s="6">
+        <v>57.832911911225601</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8">
+        <v>29.3986012905469</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="4"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="4"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="4"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/outputs/model_comparison_result.xlsx
+++ b/outputs/model_comparison_result.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="1" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="model_comparison" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
   <si>
     <t>Model</t>
   </si>
@@ -94,9 +94,6 @@
     <t>Δ Random→Walk</t>
   </si>
   <si>
-    <t>...</t>
-  </si>
-  <si>
     <t>Raw LSTM</t>
   </si>
   <si>
@@ -104,13 +101,205 @@
   </si>
   <si>
     <t>All Engineered Features LSTM</t>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>Max Prediction</t>
+  </si>
+  <si>
+    <t>Max Actual</t>
+  </si>
+  <si>
+    <t>Random</t>
+  </si>
+  <si>
+    <t>Chronological</t>
+  </si>
+  <si>
+    <t>(optional)</t>
+  </si>
+  <si>
+    <t>Training Period</t>
+  </si>
+  <si>
+    <t>2016–2017</t>
+  </si>
+  <si>
+    <t>2016–2019</t>
+  </si>
+  <si>
+    <t>2016–2021</t>
+  </si>
+  <si>
+    <t>2016–2022</t>
+  </si>
+  <si>
+    <t>2016–2024</t>
+  </si>
+  <si>
+    <t>lr</t>
+  </si>
+  <si>
+    <t>Linear RMSE</t>
+  </si>
+  <si>
+    <t>Decision Tree RMSE</t>
+  </si>
+  <si>
+    <t>rmse  by fold</t>
+  </si>
+  <si>
+    <t>LR</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>RF</t>
+  </si>
+  <si>
+    <t>XGB</t>
+  </si>
+  <si>
+    <t>wf comparison</t>
+  </si>
+  <si>
+    <t>Average MAE</t>
+  </si>
+  <si>
+    <t>Average R²</t>
+  </si>
+  <si>
+    <t>-1.87*</t>
+  </si>
+  <si>
+    <t>-0.85*</t>
+  </si>
+  <si>
+    <t>-0.87*</t>
+  </si>
+  <si>
+    <t>-1.17*</t>
+  </si>
+  <si>
+    <t>Walk-forward</t>
+  </si>
+  <si>
+    <t>random comparison</t>
+  </si>
+  <si>
+    <t>MAE</t>
+  </si>
+  <si>
+    <t>wf</t>
+  </si>
+  <si>
+    <t>Mean RMSE</t>
+  </si>
+  <si>
+    <t>Fold 1</t>
+  </si>
+  <si>
+    <t>Fold 2</t>
+  </si>
+  <si>
+    <t>Fold 3</t>
+  </si>
+  <si>
+    <t>Fold 4</t>
+  </si>
+  <si>
+    <t>Fold 5</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Very good</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Poor</t>
+  </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>Raw 50-unit RMSE</t>
+  </si>
+  <si>
+    <t>Engineered 50-unit RMSE</t>
+  </si>
+  <si>
+    <t>Engineered 100-unit RMSE</t>
+  </si>
+  <si>
+    <t>Netflix</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>lstm</t>
+  </si>
+  <si>
+    <t>LSTM</t>
+  </si>
+  <si>
+    <t>lstm wf</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Final value</t>
+  </si>
+  <si>
+    <t>Mean MAE</t>
+  </si>
+  <si>
+    <t>Median RMSE</t>
+  </si>
+  <si>
+    <t>RMSE SD</t>
+  </si>
+  <si>
+    <t>Mean R²</t>
+  </si>
+  <si>
+    <t>Walk Mean RMSE</t>
+  </si>
+  <si>
+    <t>Walk Median RMSE</t>
+  </si>
+  <si>
+    <t>An additional experiment using engineered technical indicators with the LSTM yielded a chronological RMSE of 31.13, substantially worse than the raw OHLCV LSTM (19.17). Because a walk-forward evaluation was not conducted for this configuration, it is excluded from the primary model comparison table.</t>
+  </si>
+  <si>
+    <t>RMSE Increase (Walk − Random)</t>
+  </si>
+  <si>
+    <t>Validation Inflation (%)</t>
+  </si>
+  <si>
+    <t>Walk Forward rmse Std</t>
+  </si>
+  <si>
+    <t>Overestimation Ratio (Walk/Random)</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,16 +321,66 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor theme="5" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -149,11 +388,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -169,24 +421,72 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="23">
     <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -214,24 +514,151 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -245,7 +672,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="13"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <scheme val="minor"/>
@@ -290,11 +717,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="E9:H12" totalsRowShown="0" headerRowDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="E9:H12" totalsRowShown="0" headerRowDxfId="22">
   <autoFilter ref="E9:H12"/>
   <tableColumns count="4">
-    <tableColumn id="1" name="LSTM Version" dataDxfId="17"/>
-    <tableColumn id="2" name="Units" dataDxfId="16"/>
+    <tableColumn id="1" name="LSTM Version" dataDxfId="21"/>
+    <tableColumn id="2" name="Units" dataDxfId="20"/>
     <tableColumn id="3" name="RMSE"/>
     <tableColumn id="4" name="R²"/>
   </tableColumns>
@@ -303,30 +730,40 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F8" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="A1:F8"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="Model" dataDxfId="13"/>
-    <tableColumn id="2" name="Random RMSE" dataDxfId="12"/>
-    <tableColumn id="3" name="Time RMSE" dataDxfId="11"/>
-    <tableColumn id="4" name="Walk RMSE" dataDxfId="10"/>
-    <tableColumn id="5" name="Best RMSE" dataDxfId="9"/>
-    <tableColumn id="6" name="Δ Random→Walk" dataDxfId="8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:I7" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+  <autoFilter ref="A1:I7"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="Model" dataDxfId="17"/>
+    <tableColumn id="2" name="Random RMSE" dataDxfId="16"/>
+    <tableColumn id="3" name="Time RMSE" dataDxfId="15"/>
+    <tableColumn id="4" name="Walk Mean RMSE" dataDxfId="14"/>
+    <tableColumn id="5" name="Best RMSE" dataDxfId="13"/>
+    <tableColumn id="7" name="Walk Median RMSE" dataDxfId="12"/>
+    <tableColumn id="8" name="Walk Forward rmse Std" dataDxfId="11"/>
+    <tableColumn id="9" name="RMSE Increase (Walk − Random)" dataDxfId="10">
+      <calculatedColumnFormula>ABS(B2-D2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" name="Validation Inflation (%)" dataDxfId="9">
+      <calculatedColumnFormula>((Table1[[#This Row],[Walk Mean RMSE]]-Table1[[#This Row],[Random RMSE]])/Table1[[#This Row],[Random RMSE]])*100</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table15" displayName="Table15" ref="A1:F8" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="A1:F8"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="Model" dataDxfId="5"/>
-    <tableColumn id="2" name="Random RMSE" dataDxfId="4"/>
-    <tableColumn id="3" name="Time RMSE" dataDxfId="3"/>
-    <tableColumn id="4" name="Walk RMSE" dataDxfId="2"/>
-    <tableColumn id="5" name="Best RMSE" dataDxfId="1"/>
-    <tableColumn id="6" name="Δ Random→Walk" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table15" displayName="Table15" ref="A1:G8" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G8"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Model" dataDxfId="6"/>
+    <tableColumn id="2" name="Random RMSE" dataDxfId="5"/>
+    <tableColumn id="3" name="Time RMSE" dataDxfId="4"/>
+    <tableColumn id="4" name="Walk RMSE" dataDxfId="3"/>
+    <tableColumn id="5" name="Best RMSE" dataDxfId="2"/>
+    <tableColumn id="6" name="Δ Random→Walk" dataDxfId="1"/>
+    <tableColumn id="7" name="Overestimation Ratio (Walk/Random)" dataDxfId="0">
+      <calculatedColumnFormula>(Table15[[#This Row],[Walk RMSE]]/Table15[[#This Row],[Random RMSE]])</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -782,7 +1219,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.21875" customWidth="1"/>
@@ -790,172 +1227,297 @@
     <col min="3" max="3" width="13.77734375" customWidth="1"/>
     <col min="4" max="4" width="15.5546875" customWidth="1"/>
     <col min="5" max="5" width="13.33203125" customWidth="1"/>
-    <col min="6" max="6" width="19.21875" customWidth="1"/>
+    <col min="6" max="6" width="17.88671875" customWidth="1"/>
+    <col min="7" max="7" width="23.77734375" customWidth="1"/>
+    <col min="8" max="8" width="25.109375" customWidth="1"/>
+    <col min="9" max="9" width="35" customWidth="1"/>
+    <col min="10" max="10" width="26.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="F1" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="10">
         <v>8.6024774970882891</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="10">
         <v>12.8340994729757</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="10">
         <v>10.260938786791</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="10">
         <v>8.6024774970882891</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="10">
+        <v>10.189660346687999</v>
+      </c>
+      <c r="G2" s="10">
+        <v>2.8075293782237498</v>
+      </c>
+      <c r="H2" s="10">
         <f>ABS(B2-D2)</f>
         <v>1.6584612897027107</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="I2" s="10">
+        <f>((Table1[[#This Row],[Walk Mean RMSE]]-Table1[[#This Row],[Random RMSE]])/Table1[[#This Row],[Random RMSE]])*100</f>
+        <v>19.278879721150748</v>
+      </c>
+      <c r="J2" s="16">
+        <f>(Table1[[#This Row],[Walk Mean RMSE]]/Table1[[#This Row],[Random RMSE]])</f>
+        <v>1.1927887972115074</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="10">
         <v>12.767838034677199</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="10">
         <v>29.230835798083699</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="10">
         <v>53.940100130441003</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="10">
         <v>12.767838034677199</v>
       </c>
-      <c r="F3" s="2">
-        <f t="shared" ref="F3:F6" si="0">ABS(B3-D3)</f>
+      <c r="F3" s="10">
+        <v>48.054992756353201</v>
+      </c>
+      <c r="G3" s="10">
+        <v>43.789690841114997</v>
+      </c>
+      <c r="H3" s="10">
+        <f>ABS(B3-D3)</f>
         <v>41.172262095763806</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="I3" s="10">
+        <f>((Table1[[#This Row],[Walk Mean RMSE]]-Table1[[#This Row],[Random RMSE]])/Table1[[#This Row],[Random RMSE]])*100</f>
+        <v>322.46854936552876</v>
+      </c>
+      <c r="J3" s="16">
+        <f>(Table1[[#This Row],[Walk Mean RMSE]]/Table1[[#This Row],[Random RMSE]])</f>
+        <v>4.2246854936552882</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="10">
         <v>9.1270676133805697</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="10">
         <v>16.8106414161781</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="10">
         <v>48.6558650628793</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="10">
         <v>9.1270676133805697</v>
       </c>
-      <c r="F4" s="2">
-        <f t="shared" si="0"/>
+      <c r="F4" s="10">
+        <v>36.949904429406899</v>
+      </c>
+      <c r="G4" s="10">
+        <v>44.697451073118103</v>
+      </c>
+      <c r="H4" s="10">
+        <f>ABS(B4-D4)</f>
         <v>39.528797449498732</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="I4" s="10">
+        <f>((Table1[[#This Row],[Walk Mean RMSE]]-Table1[[#This Row],[Random RMSE]])/Table1[[#This Row],[Random RMSE]])*100</f>
+        <v>433.09416697591087</v>
+      </c>
+      <c r="J4" s="16">
+        <f>(Table1[[#This Row],[Walk Mean RMSE]]/Table1[[#This Row],[Random RMSE]])</f>
+        <v>5.3309416697591088</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="10">
         <v>9.4238145778730598</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="10">
         <v>23.066939177986001</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="10">
         <v>51.9654495245303</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="10">
         <v>9.4238145778730598</v>
       </c>
-      <c r="F5" s="2">
-        <f t="shared" si="0"/>
+      <c r="F5" s="10">
+        <v>44.272708423711201</v>
+      </c>
+      <c r="G5" s="10">
+        <v>43.937501884618399</v>
+      </c>
+      <c r="H5" s="10">
+        <f>ABS(B5-D5)</f>
         <v>42.54163494665724</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="I5" s="10">
+        <f>((Table1[[#This Row],[Walk Mean RMSE]]-Table1[[#This Row],[Random RMSE]])/Table1[[#This Row],[Random RMSE]])*100</f>
+        <v>451.42690993246202</v>
+      </c>
+      <c r="J5" s="16">
+        <f>(Table1[[#This Row],[Walk Mean RMSE]]/Table1[[#This Row],[Random RMSE]])</f>
+        <v>5.5142690993246202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="10">
         <v>9.1194110478356905</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="10">
         <v>30.5753313206352</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="10">
         <v>26.099956053911399</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="10">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="F6" s="10">
+        <v>25.619568462923901</v>
+      </c>
+      <c r="G6" s="10">
+        <v>13.452844792569</v>
+      </c>
+      <c r="H6" s="10">
+        <f>ABS(B6-D6)</f>
+        <v>16.980545006075708</v>
+      </c>
+      <c r="I6" s="10">
+        <f>((Table1[[#This Row],[Walk Mean RMSE]]-Table1[[#This Row],[Random RMSE]])/Table1[[#This Row],[Random RMSE]])*100</f>
+        <v>186.20221105293527</v>
+      </c>
+      <c r="J6" s="21">
+        <f>(Table1[[#This Row],[Walk Mean RMSE]]/Table1[[#This Row],[Random RMSE]])</f>
+        <v>2.8620221105293528</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="26.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="2">
-        <f t="shared" si="0"/>
-        <v>16.980545006075708</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="2">
-        <v>19.940000000000001</v>
-      </c>
-      <c r="D7" s="6">
-        <v>57.832911911225601</v>
-      </c>
-      <c r="E7" s="2">
-        <v>19.940000000000001</v>
-      </c>
-      <c r="F7" s="6">
-        <v>57.832911911225601</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8">
-        <v>29.3986012905469</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D14" s="5"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D16" s="6"/>
+      <c r="C7" s="10">
+        <v>19.173602731126401</v>
+      </c>
+      <c r="D7" s="11">
+        <v>38.226916018566698</v>
+      </c>
+      <c r="E7" s="10">
+        <v>19.173602731126401</v>
+      </c>
+      <c r="F7" s="11">
+        <v>17.482276355088999</v>
+      </c>
+      <c r="G7" s="10">
+        <v>38.426114269864399</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="J8" s="16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="14"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="14"/>
+      <c r="V10" s="14"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="D13" s="5"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="D15" s="6"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A10:V10"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1113,7 +1675,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:Y44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
@@ -1122,9 +1684,19 @@
     <col min="4" max="4" width="14.21875" customWidth="1"/>
     <col min="5" max="5" width="13.77734375" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="23.33203125" customWidth="1"/>
+    <col min="9" max="9" width="7" customWidth="1"/>
+    <col min="10" max="10" width="13.21875" customWidth="1"/>
+    <col min="11" max="11" width="12.88671875" customWidth="1"/>
+    <col min="12" max="12" width="15.44140625" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" customWidth="1"/>
+    <col min="15" max="15" width="10.88671875" customWidth="1"/>
+    <col min="24" max="24" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1143,141 +1715,174 @@
       <c r="F1" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G1" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="18">
         <v>4.4495586506269298</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="18">
         <v>7.3314479275857503</v>
       </c>
-      <c r="D2" s="2">
-        <v>10.260938786791</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="D2" s="19">
+        <v>18.0317123755285</v>
+      </c>
+      <c r="E2" s="18">
         <v>4.4495586506269298</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="19">
         <f>ABS(B2-D2)</f>
-        <v>5.81138013616407</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>13.58215372490157</v>
+      </c>
+      <c r="G2" s="19">
+        <f>(Table15[[#This Row],[Walk RMSE]]/Table15[[#This Row],[Random RMSE]])</f>
+        <v>4.0524721194511919</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="18">
         <v>3.3807335861675001</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="18">
         <v>35.8586877169991</v>
       </c>
-      <c r="D3" s="2">
-        <v>53.940100130441003</v>
-      </c>
-      <c r="E3" s="6">
+      <c r="D3" s="19">
+        <v>23.673396335962298</v>
+      </c>
+      <c r="E3" s="18">
         <v>3.3807335861675001</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="19">
         <f t="shared" ref="F3:F6" si="0">ABS(B3-D3)</f>
-        <v>50.559366544273502</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>20.292662749794797</v>
+      </c>
+      <c r="G3" s="19">
+        <f>(Table15[[#This Row],[Walk RMSE]]/Table15[[#This Row],[Random RMSE]])</f>
+        <v>7.0024436213559094</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="18">
         <v>2.71393967817533</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="18">
         <v>37.102660473070898</v>
       </c>
-      <c r="D4" s="2">
-        <v>48.6558650628793</v>
-      </c>
-      <c r="E4" s="6">
+      <c r="D4" s="19">
+        <v>24.0148788733574</v>
+      </c>
+      <c r="E4" s="18">
         <v>2.71393967817533</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="19">
         <f t="shared" si="0"/>
-        <v>45.941925384703971</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>21.300939195182071</v>
+      </c>
+      <c r="G4" s="19">
+        <f>(Table15[[#This Row],[Walk RMSE]]/Table15[[#This Row],[Random RMSE]])</f>
+        <v>8.8487150493718367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="19">
+        <v>2.9195659452826801</v>
+      </c>
+      <c r="C5" s="19">
+        <v>40.547192929993699</v>
+      </c>
+      <c r="D5" s="19">
+        <v>26.210680113662701</v>
+      </c>
+      <c r="E5" s="19">
         <v>9.4238145778730598</v>
       </c>
-      <c r="C5" s="2">
-        <v>23.066939177986001</v>
-      </c>
-      <c r="D5" s="2">
-        <v>51.9654495245303</v>
-      </c>
-      <c r="E5" s="2">
-        <v>9.4238145778730598</v>
-      </c>
-      <c r="F5" s="2">
+      <c r="F5" s="19">
         <f t="shared" si="0"/>
-        <v>42.54163494665724</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>23.29111416838002</v>
+      </c>
+      <c r="G5" s="19">
+        <f>(Table15[[#This Row],[Walk RMSE]]/Table15[[#This Row],[Random RMSE]])</f>
+        <v>8.9775948222758544</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="2">
-        <v>9.1194110478356905</v>
-      </c>
-      <c r="C6" s="2">
-        <v>30.5753313206352</v>
-      </c>
-      <c r="D6" s="2">
-        <v>26.099956053911399</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="B6" s="19">
+        <v>2.7944868472688298</v>
+      </c>
+      <c r="C6" s="19">
+        <v>4.9839904635054904</v>
+      </c>
+      <c r="D6" s="18">
+        <v>9.9364874466985498</v>
+      </c>
+      <c r="E6" s="19">
+        <v>2.7944868472688298</v>
+      </c>
+      <c r="F6" s="19">
+        <f t="shared" si="0"/>
+        <v>7.1420005994297195</v>
+      </c>
+      <c r="G6" s="19">
+        <f>(Table15[[#This Row],[Walk RMSE]]/Table15[[#This Row],[Random RMSE]])</f>
+        <v>3.555746721946428</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="2">
-        <f t="shared" si="0"/>
-        <v>16.980545006075708</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="19">
+        <v>19.940000000000001</v>
+      </c>
+      <c r="D7" s="18">
+        <v>57.832911911225601</v>
+      </c>
+      <c r="E7" s="19">
+        <v>19.940000000000001</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="2">
-        <v>19.940000000000001</v>
-      </c>
-      <c r="D7" s="6">
-        <v>57.832911911225601</v>
-      </c>
-      <c r="E7" s="2">
-        <v>19.940000000000001</v>
-      </c>
-      <c r="F7" s="6">
-        <v>57.832911911225601</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20">
         <v>29.3986012905469</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1285,56 +1890,984 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
+      <c r="I10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2">
+        <v>4.45</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.99619999999999997</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="2">
+        <v>14.64</v>
+      </c>
+      <c r="L12" s="2">
+        <v>-8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="2">
+        <v>7.33</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.93340000000000001</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="2">
+        <v>286.19</v>
+      </c>
+      <c r="I13" s="4">
+        <v>2</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13" s="2">
+        <v>56.38</v>
+      </c>
+      <c r="L13" s="2">
+        <v>-3.36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3.38</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.99780000000000002</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="4">
+        <v>3</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="2">
+        <v>6.46</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0.83199999999999996</v>
+      </c>
+      <c r="O14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="2">
+        <v>35.86</v>
+      </c>
+      <c r="D15" s="2">
+        <v>-0.59409999999999996</v>
+      </c>
+      <c r="E15" s="3">
+        <v>195.72</v>
+      </c>
+      <c r="F15" s="3">
+        <v>286.19</v>
+      </c>
+      <c r="I15" s="4">
+        <v>4</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K15" s="2">
+        <v>4.83</v>
+      </c>
+      <c r="L15" s="2">
+        <v>0.93200000000000005</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2.71</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.99860000000000004</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="4">
+        <v>5</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="2">
+        <v>7.84</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0.88200000000000001</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="P16" s="2">
+        <v>18.03</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>14.64</v>
+      </c>
+      <c r="R16" s="2">
+        <v>56.38</v>
+      </c>
+      <c r="S16" s="2">
+        <v>6.46</v>
+      </c>
+      <c r="T16" s="2">
+        <v>4.83</v>
+      </c>
+      <c r="U16" s="2">
+        <v>7.84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="2">
+        <v>37.1</v>
+      </c>
+      <c r="D17" s="2">
+        <v>-0.70660000000000001</v>
+      </c>
+      <c r="E17" s="3">
+        <v>195.35</v>
+      </c>
+      <c r="F17" s="3">
+        <v>286.19</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="P17" s="2">
+        <v>23.67</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="R17" s="2">
+        <v>43.05</v>
+      </c>
+      <c r="S17" s="2">
+        <v>20.55</v>
+      </c>
+      <c r="T17" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="U17" s="2">
+        <v>39.369999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="O18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="2">
+        <v>24.01</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>6.02</v>
+      </c>
+      <c r="R18" s="2">
+        <v>43.44</v>
+      </c>
+      <c r="S18" s="2">
+        <v>20.54</v>
+      </c>
+      <c r="T18" s="2">
+        <v>9.33</v>
+      </c>
+      <c r="U18" s="2">
+        <v>40.74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="O19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="P19" s="2">
+        <v>26.21</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>6.11</v>
+      </c>
+      <c r="R19" s="2">
+        <v>44.56</v>
+      </c>
+      <c r="S19" s="2">
+        <v>21.6</v>
+      </c>
+      <c r="T19" s="2">
+        <v>12.67</v>
+      </c>
+      <c r="U19" s="2">
+        <v>46.11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="P20" s="3">
+        <v>9.94</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>19.48</v>
+      </c>
+      <c r="R20" s="2">
+        <v>14.73</v>
+      </c>
+      <c r="S20" s="2">
+        <v>6.23</v>
+      </c>
+      <c r="T20" s="2">
+        <v>2.92</v>
+      </c>
+      <c r="U20" s="2">
+        <v>6.32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="J21" s="2">
+        <v>1</v>
+      </c>
+      <c r="K21" s="2">
+        <v>14.64</v>
+      </c>
+      <c r="L21" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="O21" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="P21" s="2">
+        <v>14.44</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>2.17</v>
+      </c>
+      <c r="R21" s="2">
+        <v>38.22</v>
+      </c>
+      <c r="S21" s="2">
+        <v>19.16</v>
+      </c>
+      <c r="T21" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="U21" s="2">
+        <v>8.44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="J22" s="2">
+        <v>2</v>
+      </c>
+      <c r="K22" s="2">
+        <v>56.38</v>
+      </c>
+      <c r="L22" s="3">
+        <v>43.05</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="J23" s="2">
+        <v>3</v>
+      </c>
+      <c r="K23" s="3">
+        <v>6.46</v>
+      </c>
+      <c r="L23" s="2">
+        <v>20.55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="J24" s="2">
+        <v>4</v>
+      </c>
+      <c r="K24" s="3">
+        <v>4.83</v>
+      </c>
+      <c r="L24" s="2">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="J25" s="2">
+        <v>5</v>
+      </c>
+      <c r="K25" s="3">
+        <v>7.84</v>
+      </c>
+      <c r="L25" s="2">
+        <v>39.369999999999997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="R26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="R27" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="S27" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="T27" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="U27" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>48</v>
+      </c>
+      <c r="R28" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="S28" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="T28" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="U28" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="X28" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G29" t="s">
+        <v>43</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R29" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="S29" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="T29" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="U29" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="3">
+        <v>15.75</v>
+      </c>
+      <c r="C30" s="3">
+        <v>18.03</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O30" s="2">
+        <v>4.45</v>
+      </c>
+      <c r="R30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S30" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="T30" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="U30" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="X30" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" s="2">
+        <v>18.96</v>
+      </c>
+      <c r="C31" s="2">
+        <v>23.67</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2">
+        <v>14.64</v>
+      </c>
+      <c r="I31" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="J31" s="3">
+        <v>6.02</v>
+      </c>
+      <c r="K31" s="3">
+        <v>6.11</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O31" s="2">
+        <v>3.38</v>
+      </c>
+      <c r="R31" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="S31" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="T31" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="U31" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="X31" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>14.44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="2">
+        <v>19.27</v>
+      </c>
+      <c r="C32" s="2">
+        <v>24.01</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" s="2">
+        <v>2</v>
+      </c>
+      <c r="H32" s="2">
+        <v>56.38</v>
+      </c>
+      <c r="I32" s="3">
+        <v>43.05</v>
+      </c>
+      <c r="J32" s="3">
+        <v>43.44</v>
+      </c>
+      <c r="K32" s="3">
+        <v>44.56</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O32" s="3">
+        <v>2.71</v>
+      </c>
+      <c r="X32" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>8.44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="2">
+        <v>21.45</v>
+      </c>
+      <c r="C33" s="3">
+        <v>26.21</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33" s="2">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3">
+        <v>6.46</v>
+      </c>
+      <c r="I33" s="2">
+        <v>20.55</v>
+      </c>
+      <c r="J33" s="2">
+        <v>20.54</v>
+      </c>
+      <c r="K33" s="2">
+        <v>21.6</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O33" s="3">
+        <v>2.92</v>
+      </c>
+      <c r="X33" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>13.26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G34" s="2">
+        <v>4</v>
+      </c>
+      <c r="H34" s="3">
+        <v>4.83</v>
+      </c>
+      <c r="I34" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="J34" s="2">
+        <v>9.33</v>
+      </c>
+      <c r="K34" s="2">
+        <v>12.67</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O34" s="3">
+        <v>7.33</v>
+      </c>
+      <c r="X34" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0.223</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="G35" s="2">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3">
+        <v>7.84</v>
+      </c>
+      <c r="I35" s="2">
+        <v>39.369999999999997</v>
+      </c>
+      <c r="J35" s="2">
+        <v>40.74</v>
+      </c>
+      <c r="K35" s="2">
+        <v>46.11</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O35" s="2">
+        <v>35.86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M36" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O36" s="2">
+        <v>37.1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="M37" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O37" s="2">
+        <v>40.549999999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>56</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O38" s="3">
+        <v>18.03</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N39" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O39" s="2">
+        <v>23.67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B40" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="2">
+        <v>3.27</v>
+      </c>
+      <c r="D40" s="2">
+        <v>4.45</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.99619999999999997</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N40" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O40" s="2">
+        <v>24.01</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="B41" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="2">
+        <v>2.15</v>
+      </c>
+      <c r="D41" s="2">
+        <v>3.38</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.99780000000000002</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H41" s="3">
+        <v>19.170000000000002</v>
+      </c>
+      <c r="I41" s="2">
+        <v>31.13</v>
+      </c>
+      <c r="J41" s="2">
+        <v>26.87</v>
+      </c>
+      <c r="M41" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N41" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O41" s="2">
+        <v>26.21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="B42" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1.69</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2.71</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0.99860000000000004</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H42" s="3">
+        <v>18.510000000000002</v>
+      </c>
+      <c r="I42" s="2">
+        <v>19.46</v>
+      </c>
+      <c r="J42" s="2">
+        <v>24.74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="B43" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1.88</v>
+      </c>
+      <c r="D43" s="2">
+        <v>2.92</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0.99839999999999995</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="B44" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="3">
+        <v>1.82</v>
+      </c>
+      <c r="D44" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0.99850000000000005</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/outputs/model_comparison_result.xlsx
+++ b/outputs/model_comparison_result.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="model_comparison" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
   <si>
     <t>Model</t>
   </si>
@@ -91,18 +91,12 @@
     <t>Best RMSE</t>
   </si>
   <si>
-    <t>Δ Random→Walk</t>
-  </si>
-  <si>
     <t>Raw LSTM</t>
   </si>
   <si>
     <t>—</t>
   </si>
   <si>
-    <t>All Engineered Features LSTM</t>
-  </si>
-  <si>
     <t>Validation</t>
   </si>
   <si>
@@ -292,14 +286,20 @@
     <t>Overestimation Ratio (Walk/Random)</t>
   </si>
   <si>
-    <t>-</t>
+    <t>NaN</t>
+  </si>
+  <si>
+    <t>Random Rank</t>
+  </si>
+  <si>
+    <t>Walk-Forward Rank</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -337,15 +337,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="13"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -353,14 +345,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="0"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -369,18 +361,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor theme="5" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -401,11 +387,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -427,258 +428,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -717,55 +487,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="E9:H12" totalsRowShown="0" headerRowDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="E9:H12" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="E9:H12"/>
   <tableColumns count="4">
-    <tableColumn id="1" name="LSTM Version" dataDxfId="21"/>
-    <tableColumn id="2" name="Units" dataDxfId="20"/>
+    <tableColumn id="1" name="LSTM Version" dataDxfId="1"/>
+    <tableColumn id="2" name="Units" dataDxfId="0"/>
     <tableColumn id="3" name="RMSE"/>
     <tableColumn id="4" name="R²"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:I7" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
-  <autoFilter ref="A1:I7"/>
-  <tableColumns count="9">
-    <tableColumn id="1" name="Model" dataDxfId="17"/>
-    <tableColumn id="2" name="Random RMSE" dataDxfId="16"/>
-    <tableColumn id="3" name="Time RMSE" dataDxfId="15"/>
-    <tableColumn id="4" name="Walk Mean RMSE" dataDxfId="14"/>
-    <tableColumn id="5" name="Best RMSE" dataDxfId="13"/>
-    <tableColumn id="7" name="Walk Median RMSE" dataDxfId="12"/>
-    <tableColumn id="8" name="Walk Forward rmse Std" dataDxfId="11"/>
-    <tableColumn id="9" name="RMSE Increase (Walk − Random)" dataDxfId="10">
-      <calculatedColumnFormula>ABS(B2-D2)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="10" name="Validation Inflation (%)" dataDxfId="9">
-      <calculatedColumnFormula>((Table1[[#This Row],[Walk Mean RMSE]]-Table1[[#This Row],[Random RMSE]])/Table1[[#This Row],[Random RMSE]])*100</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table15" displayName="Table15" ref="A1:G8" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G8"/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="Model" dataDxfId="6"/>
-    <tableColumn id="2" name="Random RMSE" dataDxfId="5"/>
-    <tableColumn id="3" name="Time RMSE" dataDxfId="4"/>
-    <tableColumn id="4" name="Walk RMSE" dataDxfId="3"/>
-    <tableColumn id="5" name="Best RMSE" dataDxfId="2"/>
-    <tableColumn id="6" name="Δ Random→Walk" dataDxfId="1"/>
-    <tableColumn id="7" name="Overestimation Ratio (Walk/Random)" dataDxfId="0">
-      <calculatedColumnFormula>(Table15[[#This Row],[Walk RMSE]]/Table15[[#This Row],[Random RMSE]])</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1219,7 +949,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.21875" customWidth="1"/>
@@ -1232,255 +962,258 @@
     <col min="8" max="8" width="25.109375" customWidth="1"/>
     <col min="9" max="9" width="35" customWidth="1"/>
     <col min="10" max="10" width="26.88671875" customWidth="1"/>
+    <col min="11" max="11" width="27.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:22" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="12"/>
+      <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="J1" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12">
+        <v>0</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="13">
+        <v>8.6</v>
+      </c>
+      <c r="D2" s="13">
+        <v>12.83</v>
+      </c>
+      <c r="E2" s="13">
+        <v>10.26</v>
+      </c>
+      <c r="F2" s="13">
+        <v>8.6</v>
+      </c>
+      <c r="G2" s="13">
+        <v>10.19</v>
+      </c>
+      <c r="H2" s="13">
+        <v>2.81</v>
+      </c>
+      <c r="I2" s="13">
+        <v>1.66</v>
+      </c>
+      <c r="J2" s="13">
+        <v>19.28</v>
+      </c>
+      <c r="K2" s="13">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="12">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="13">
+        <v>12.77</v>
+      </c>
+      <c r="D3" s="13">
+        <v>29.23</v>
+      </c>
+      <c r="E3" s="13">
+        <v>53.94</v>
+      </c>
+      <c r="F3" s="13">
+        <v>12.77</v>
+      </c>
+      <c r="G3" s="13">
+        <v>48.05</v>
+      </c>
+      <c r="H3" s="13">
+        <v>43.79</v>
+      </c>
+      <c r="I3" s="13">
+        <v>41.17</v>
+      </c>
+      <c r="J3" s="13">
+        <v>322.47000000000003</v>
+      </c>
+      <c r="K3" s="13">
+        <v>4.22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="13">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="D4" s="13">
+        <v>16.809999999999999</v>
+      </c>
+      <c r="E4" s="13">
+        <v>48.66</v>
+      </c>
+      <c r="F4" s="13">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="G4" s="13">
+        <v>36.950000000000003</v>
+      </c>
+      <c r="H4" s="13">
+        <v>44.7</v>
+      </c>
+      <c r="I4" s="13">
+        <v>39.53</v>
+      </c>
+      <c r="J4" s="13">
+        <v>433.09</v>
+      </c>
+      <c r="K4" s="13">
+        <v>5.33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="13">
+        <v>9.42</v>
+      </c>
+      <c r="D5" s="13">
+        <v>23.07</v>
+      </c>
+      <c r="E5" s="13">
+        <v>51.97</v>
+      </c>
+      <c r="F5" s="13">
+        <v>9.42</v>
+      </c>
+      <c r="G5" s="13">
+        <v>44.27</v>
+      </c>
+      <c r="H5" s="13">
+        <v>43.94</v>
+      </c>
+      <c r="I5" s="13">
+        <v>42.54</v>
+      </c>
+      <c r="J5" s="13">
+        <v>451.43</v>
+      </c>
+      <c r="K5" s="13">
+        <v>5.51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="13">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="D6" s="13">
+        <v>30.58</v>
+      </c>
+      <c r="E6" s="13">
+        <v>26.1</v>
+      </c>
+      <c r="F6" s="13">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="G6" s="13">
+        <v>25.62</v>
+      </c>
+      <c r="H6" s="13">
+        <v>13.45</v>
+      </c>
+      <c r="I6" s="13">
+        <v>16.98</v>
+      </c>
+      <c r="J6" s="13">
+        <v>186.2</v>
+      </c>
+      <c r="K6" s="13">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="12">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10">
-        <v>8.6024774970882891</v>
-      </c>
-      <c r="C2" s="10">
-        <v>12.8340994729757</v>
-      </c>
-      <c r="D2" s="10">
-        <v>10.260938786791</v>
-      </c>
-      <c r="E2" s="10">
-        <v>8.6024774970882891</v>
-      </c>
-      <c r="F2" s="10">
-        <v>10.189660346687999</v>
-      </c>
-      <c r="G2" s="10">
-        <v>2.8075293782237498</v>
-      </c>
-      <c r="H2" s="10">
-        <f>ABS(B2-D2)</f>
-        <v>1.6584612897027107</v>
-      </c>
-      <c r="I2" s="10">
-        <f>((Table1[[#This Row],[Walk Mean RMSE]]-Table1[[#This Row],[Random RMSE]])/Table1[[#This Row],[Random RMSE]])*100</f>
-        <v>19.278879721150748</v>
-      </c>
-      <c r="J2" s="16">
-        <f>(Table1[[#This Row],[Walk Mean RMSE]]/Table1[[#This Row],[Random RMSE]])</f>
-        <v>1.1927887972115074</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="10">
-        <v>12.767838034677199</v>
-      </c>
-      <c r="C3" s="10">
-        <v>29.230835798083699</v>
-      </c>
-      <c r="D3" s="10">
-        <v>53.940100130441003</v>
-      </c>
-      <c r="E3" s="10">
-        <v>12.767838034677199</v>
-      </c>
-      <c r="F3" s="10">
-        <v>48.054992756353201</v>
-      </c>
-      <c r="G3" s="10">
-        <v>43.789690841114997</v>
-      </c>
-      <c r="H3" s="10">
-        <f>ABS(B3-D3)</f>
-        <v>41.172262095763806</v>
-      </c>
-      <c r="I3" s="10">
-        <f>((Table1[[#This Row],[Walk Mean RMSE]]-Table1[[#This Row],[Random RMSE]])/Table1[[#This Row],[Random RMSE]])*100</f>
-        <v>322.46854936552876</v>
-      </c>
-      <c r="J3" s="16">
-        <f>(Table1[[#This Row],[Walk Mean RMSE]]/Table1[[#This Row],[Random RMSE]])</f>
-        <v>4.2246854936552882</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="10">
-        <v>9.1270676133805697</v>
-      </c>
-      <c r="C4" s="10">
-        <v>16.8106414161781</v>
-      </c>
-      <c r="D4" s="10">
-        <v>48.6558650628793</v>
-      </c>
-      <c r="E4" s="10">
-        <v>9.1270676133805697</v>
-      </c>
-      <c r="F4" s="10">
-        <v>36.949904429406899</v>
-      </c>
-      <c r="G4" s="10">
-        <v>44.697451073118103</v>
-      </c>
-      <c r="H4" s="10">
-        <f>ABS(B4-D4)</f>
-        <v>39.528797449498732</v>
-      </c>
-      <c r="I4" s="10">
-        <f>((Table1[[#This Row],[Walk Mean RMSE]]-Table1[[#This Row],[Random RMSE]])/Table1[[#This Row],[Random RMSE]])*100</f>
-        <v>433.09416697591087</v>
-      </c>
-      <c r="J4" s="16">
-        <f>(Table1[[#This Row],[Walk Mean RMSE]]/Table1[[#This Row],[Random RMSE]])</f>
-        <v>5.3309416697591088</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="10">
-        <v>9.4238145778730598</v>
-      </c>
-      <c r="C5" s="10">
-        <v>23.066939177986001</v>
-      </c>
-      <c r="D5" s="10">
-        <v>51.9654495245303</v>
-      </c>
-      <c r="E5" s="10">
-        <v>9.4238145778730598</v>
-      </c>
-      <c r="F5" s="10">
-        <v>44.272708423711201</v>
-      </c>
-      <c r="G5" s="10">
-        <v>43.937501884618399</v>
-      </c>
-      <c r="H5" s="10">
-        <f>ABS(B5-D5)</f>
-        <v>42.54163494665724</v>
-      </c>
-      <c r="I5" s="10">
-        <f>((Table1[[#This Row],[Walk Mean RMSE]]-Table1[[#This Row],[Random RMSE]])/Table1[[#This Row],[Random RMSE]])*100</f>
-        <v>451.42690993246202</v>
-      </c>
-      <c r="J5" s="16">
-        <f>(Table1[[#This Row],[Walk Mean RMSE]]/Table1[[#This Row],[Random RMSE]])</f>
-        <v>5.5142690993246202</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="10">
-        <v>9.1194110478356905</v>
-      </c>
-      <c r="C6" s="10">
-        <v>30.5753313206352</v>
-      </c>
-      <c r="D6" s="10">
-        <v>26.099956053911399</v>
-      </c>
-      <c r="E6" s="10">
-        <v>9.1199999999999992</v>
-      </c>
-      <c r="F6" s="10">
-        <v>25.619568462923901</v>
-      </c>
-      <c r="G6" s="10">
-        <v>13.452844792569</v>
-      </c>
-      <c r="H6" s="10">
-        <f>ABS(B6-D6)</f>
-        <v>16.980545006075708</v>
-      </c>
-      <c r="I6" s="10">
-        <f>((Table1[[#This Row],[Walk Mean RMSE]]-Table1[[#This Row],[Random RMSE]])/Table1[[#This Row],[Random RMSE]])*100</f>
-        <v>186.20221105293527</v>
-      </c>
-      <c r="J6" s="21">
-        <f>(Table1[[#This Row],[Walk Mean RMSE]]/Table1[[#This Row],[Random RMSE]])</f>
-        <v>2.8620221105293528</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="26.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="10">
-        <v>19.173602731126401</v>
-      </c>
-      <c r="D7" s="11">
-        <v>38.226916018566698</v>
-      </c>
-      <c r="E7" s="10">
-        <v>19.173602731126401</v>
-      </c>
-      <c r="F7" s="11">
-        <v>17.482276355088999</v>
-      </c>
-      <c r="G7" s="10">
-        <v>38.426114269864399</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>91</v>
+      <c r="D7" s="13">
+        <v>19.170000000000002</v>
+      </c>
+      <c r="E7" s="13">
+        <v>38.229999999999997</v>
+      </c>
+      <c r="F7" s="13">
+        <v>19.170000000000002</v>
+      </c>
+      <c r="G7" s="13">
+        <v>17.48</v>
+      </c>
+      <c r="H7" s="13">
+        <v>38.43</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="J8" s="16" t="s">
-        <v>91</v>
-      </c>
+      <c r="J8" s="9"/>
     </row>
     <row r="10" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
@@ -1510,15 +1243,78 @@
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D15" s="6"/>
     </row>
+    <row r="20" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="5:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E21" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="2">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="5:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E23" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="2">
+        <v>3</v>
+      </c>
+      <c r="G23" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="2">
+        <v>4</v>
+      </c>
+      <c r="G24" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E25" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" s="2">
+        <v>5</v>
+      </c>
+      <c r="G25" s="2">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A10:V10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -1685,9 +1481,9 @@
     <col min="5" max="5" width="13.77734375" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="23.33203125" customWidth="1"/>
-    <col min="9" max="9" width="7" customWidth="1"/>
-    <col min="10" max="10" width="13.21875" customWidth="1"/>
-    <col min="11" max="11" width="12.88671875" customWidth="1"/>
+    <col min="9" max="9" width="16.44140625" customWidth="1"/>
+    <col min="10" max="10" width="27.21875" customWidth="1"/>
+    <col min="11" max="11" width="20.33203125" customWidth="1"/>
     <col min="12" max="12" width="15.44140625" customWidth="1"/>
     <col min="13" max="13" width="13.33203125" customWidth="1"/>
     <col min="14" max="14" width="14.6640625" customWidth="1"/>
@@ -1696,191 +1492,311 @@
     <col min="25" max="25" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="12"/>
+      <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="12">
+        <v>0</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="13">
+        <v>4.45</v>
+      </c>
+      <c r="D2" s="13">
+        <v>7.33</v>
+      </c>
+      <c r="E2" s="13">
+        <v>18.03</v>
+      </c>
+      <c r="F2" s="13">
+        <v>4.45</v>
+      </c>
+      <c r="G2" s="13">
+        <v>7.84</v>
+      </c>
+      <c r="H2" s="13">
+        <v>19.47</v>
+      </c>
+      <c r="I2" s="13">
+        <v>13.58</v>
+      </c>
+      <c r="J2" s="13">
+        <v>305.25</v>
+      </c>
+      <c r="K2" s="13">
+        <v>4.05</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="12">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="13">
+        <v>3.38</v>
+      </c>
+      <c r="D3" s="13">
+        <v>35.86</v>
+      </c>
+      <c r="E3" s="13">
+        <v>23.67</v>
+      </c>
+      <c r="F3" s="13">
+        <v>3.38</v>
+      </c>
+      <c r="G3" s="13">
+        <v>20.55</v>
+      </c>
+      <c r="H3" s="13">
+        <v>15.14</v>
+      </c>
+      <c r="I3" s="13">
+        <v>20.29</v>
+      </c>
+      <c r="J3" s="13">
+        <v>600.24</v>
+      </c>
+      <c r="K3" s="13">
+        <v>7</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O3" s="2">
+        <v>1</v>
+      </c>
+      <c r="P3" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="12">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="13">
+        <v>2.71</v>
+      </c>
+      <c r="D4" s="13">
+        <v>37.1</v>
+      </c>
+      <c r="E4" s="13">
+        <v>24.01</v>
+      </c>
+      <c r="F4" s="13">
+        <v>2.71</v>
+      </c>
+      <c r="G4" s="13">
+        <v>20.54</v>
+      </c>
+      <c r="H4" s="13">
+        <v>15.55</v>
+      </c>
+      <c r="I4" s="13">
+        <v>21.3</v>
+      </c>
+      <c r="J4" s="13">
+        <v>784.87</v>
+      </c>
+      <c r="K4" s="13">
+        <v>8.85</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" s="2">
+        <v>2</v>
+      </c>
+      <c r="P4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="12">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="13">
+        <v>2.92</v>
+      </c>
+      <c r="D5" s="13">
+        <v>40.549999999999997</v>
+      </c>
+      <c r="E5" s="13">
+        <v>26.21</v>
+      </c>
+      <c r="F5" s="13">
+        <v>2.92</v>
+      </c>
+      <c r="G5" s="13">
+        <v>21.6</v>
+      </c>
+      <c r="H5" s="13">
+        <v>16.38</v>
+      </c>
+      <c r="I5" s="13">
+        <v>23.29</v>
+      </c>
+      <c r="J5" s="13">
+        <v>797.76</v>
+      </c>
+      <c r="K5" s="13">
+        <v>8.98</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="O5" s="2">
+        <v>3</v>
+      </c>
+      <c r="P5" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="12">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="13">
+        <v>2.79</v>
+      </c>
+      <c r="D6" s="13">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="E6" s="13">
+        <v>9.94</v>
+      </c>
+      <c r="F6" s="13">
+        <v>2.79</v>
+      </c>
+      <c r="G6" s="13">
+        <v>6.32</v>
+      </c>
+      <c r="H6" s="13">
+        <v>6.17</v>
+      </c>
+      <c r="I6" s="13">
+        <v>7.14</v>
+      </c>
+      <c r="J6" s="13">
+        <v>255.57</v>
+      </c>
+      <c r="K6" s="13">
+        <v>3.56</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="O6" s="2">
+        <v>4</v>
+      </c>
+      <c r="P6" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="12">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="C7" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="13">
+        <v>18.510000000000002</v>
+      </c>
+      <c r="E7" s="13">
+        <v>14.44</v>
+      </c>
+      <c r="F7" s="13">
+        <v>14.44</v>
+      </c>
+      <c r="G7" s="13">
+        <v>8.44</v>
+      </c>
+      <c r="H7" s="13">
+        <v>13.26</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="N7" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18">
-        <v>4.4495586506269298</v>
-      </c>
-      <c r="C2" s="18">
-        <v>7.3314479275857503</v>
-      </c>
-      <c r="D2" s="19">
-        <v>18.0317123755285</v>
-      </c>
-      <c r="E2" s="18">
-        <v>4.4495586506269298</v>
-      </c>
-      <c r="F2" s="19">
-        <f>ABS(B2-D2)</f>
-        <v>13.58215372490157</v>
-      </c>
-      <c r="G2" s="19">
-        <f>(Table15[[#This Row],[Walk RMSE]]/Table15[[#This Row],[Random RMSE]])</f>
-        <v>4.0524721194511919</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="O7" s="2">
+        <v>5</v>
+      </c>
+      <c r="P7" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="18">
-        <v>3.3807335861675001</v>
-      </c>
-      <c r="C3" s="18">
-        <v>35.8586877169991</v>
-      </c>
-      <c r="D3" s="19">
-        <v>23.673396335962298</v>
-      </c>
-      <c r="E3" s="18">
-        <v>3.3807335861675001</v>
-      </c>
-      <c r="F3" s="19">
-        <f t="shared" ref="F3:F6" si="0">ABS(B3-D3)</f>
-        <v>20.292662749794797</v>
-      </c>
-      <c r="G3" s="19">
-        <f>(Table15[[#This Row],[Walk RMSE]]/Table15[[#This Row],[Random RMSE]])</f>
-        <v>7.0024436213559094</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="18">
-        <v>2.71393967817533</v>
-      </c>
-      <c r="C4" s="18">
-        <v>37.102660473070898</v>
-      </c>
-      <c r="D4" s="19">
-        <v>24.0148788733574</v>
-      </c>
-      <c r="E4" s="18">
-        <v>2.71393967817533</v>
-      </c>
-      <c r="F4" s="19">
-        <f t="shared" si="0"/>
-        <v>21.300939195182071</v>
-      </c>
-      <c r="G4" s="19">
-        <f>(Table15[[#This Row],[Walk RMSE]]/Table15[[#This Row],[Random RMSE]])</f>
-        <v>8.8487150493718367</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="19">
-        <v>2.9195659452826801</v>
-      </c>
-      <c r="C5" s="19">
-        <v>40.547192929993699</v>
-      </c>
-      <c r="D5" s="19">
-        <v>26.210680113662701</v>
-      </c>
-      <c r="E5" s="19">
-        <v>9.4238145778730598</v>
-      </c>
-      <c r="F5" s="19">
-        <f t="shared" si="0"/>
-        <v>23.29111416838002</v>
-      </c>
-      <c r="G5" s="19">
-        <f>(Table15[[#This Row],[Walk RMSE]]/Table15[[#This Row],[Random RMSE]])</f>
-        <v>8.9775948222758544</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="19">
-        <v>2.7944868472688298</v>
-      </c>
-      <c r="C6" s="19">
-        <v>4.9839904635054904</v>
-      </c>
-      <c r="D6" s="18">
-        <v>9.9364874466985498</v>
-      </c>
-      <c r="E6" s="19">
-        <v>2.7944868472688298</v>
-      </c>
-      <c r="F6" s="19">
-        <f t="shared" si="0"/>
-        <v>7.1420005994297195</v>
-      </c>
-      <c r="G6" s="19">
-        <f>(Table15[[#This Row],[Walk RMSE]]/Table15[[#This Row],[Random RMSE]])</f>
-        <v>3.555746721946428</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="19">
-        <v>19.940000000000001</v>
-      </c>
-      <c r="D7" s="18">
-        <v>57.832911911225601</v>
-      </c>
-      <c r="E7" s="19">
-        <v>19.940000000000001</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20">
-        <v>29.3986012905469</v>
-      </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="19" t="s">
-        <v>91</v>
-      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="4"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1898,7 +1814,7 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="I10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
@@ -1906,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>19</v>
@@ -1915,16 +1831,16 @@
         <v>20</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>19</v>
@@ -1938,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" s="2">
         <v>4.45</v>
@@ -1947,16 +1863,16 @@
         <v>0.99619999999999997</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K12" s="2">
         <v>14.64</v>
@@ -1970,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2">
         <v>7.33</v>
@@ -1979,7 +1895,7 @@
         <v>0.93340000000000001</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F13" s="2">
         <v>286.19</v>
@@ -1988,7 +1904,7 @@
         <v>2</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K13" s="2">
         <v>56.38</v>
@@ -2002,7 +1918,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C14" s="2">
         <v>3.38</v>
@@ -2011,16 +1927,16 @@
         <v>0.99780000000000002</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I14" s="4">
         <v>3</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K14" s="2">
         <v>6.46</v>
@@ -2029,7 +1945,7 @@
         <v>0.83199999999999996</v>
       </c>
       <c r="O14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
@@ -2037,7 +1953,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C15" s="2">
         <v>35.86</v>
@@ -2055,7 +1971,7 @@
         <v>4</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K15" s="2">
         <v>4.83</v>
@@ -2067,22 +1983,22 @@
         <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="R15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="Q15" s="3" t="s">
+      <c r="S15" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="R15" s="3" t="s">
+      <c r="T15" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S15" s="3" t="s">
+      <c r="U15" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
@@ -2090,7 +2006,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C16" s="2">
         <v>2.71</v>
@@ -2099,16 +2015,16 @@
         <v>0.99860000000000004</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I16" s="4">
         <v>5</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K16" s="2">
         <v>7.84</v>
@@ -2143,7 +2059,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C17" s="2">
         <v>37.1</v>
@@ -2230,10 +2146,10 @@
         <v>4</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="O20" s="8" t="s">
         <v>16</v>
@@ -2268,7 +2184,7 @@
         <v>6.3</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P21" s="2">
         <v>14.44</v>
@@ -2338,13 +2254,13 @@
         <v>0</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
@@ -2352,33 +2268,33 @@
         <v>1</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T27" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="U27" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="R28" s="4" t="s">
         <v>2</v>
       </c>
       <c r="S28" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T28" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="U28" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="X28" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
@@ -2386,22 +2302,22 @@
         <v>0</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G29" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>19</v>
@@ -2410,19 +2326,19 @@
         <v>3</v>
       </c>
       <c r="S29" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T29" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="U29" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="X29" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Y29" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
@@ -2436,28 +2352,28 @@
         <v>18.03</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="K30" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="M30" s="4" t="s">
         <v>1</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O30" s="2">
         <v>4.45</v>
@@ -2466,16 +2382,16 @@
         <v>15</v>
       </c>
       <c r="S30" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T30" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="U30" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="X30" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Y30" s="3">
         <v>11.4</v>
@@ -2492,7 +2408,7 @@
         <v>23.67</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -2513,7 +2429,7 @@
         <v>2</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O31" s="2">
         <v>3.38</v>
@@ -2522,16 +2438,16 @@
         <v>16</v>
       </c>
       <c r="S31" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T31" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="U31" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="X31" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Y31" s="3">
         <v>14.44</v>
@@ -2548,7 +2464,7 @@
         <v>24.01</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G32" s="2">
         <v>2</v>
@@ -2569,13 +2485,13 @@
         <v>3</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O32" s="3">
         <v>2.71</v>
       </c>
       <c r="X32" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="Y32" s="3">
         <v>8.44</v>
@@ -2592,7 +2508,7 @@
         <v>26.21</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G33" s="2">
         <v>3</v>
@@ -2613,13 +2529,13 @@
         <v>15</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O33" s="3">
         <v>2.92</v>
       </c>
       <c r="X33" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="Y33" s="3">
         <v>13.26</v>
@@ -2645,13 +2561,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O34" s="3">
         <v>7.33</v>
       </c>
       <c r="X34" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Y34" s="3">
         <v>0.223</v>
@@ -2677,7 +2593,7 @@
         <v>2</v>
       </c>
       <c r="N35" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O35" s="2">
         <v>35.86</v>
@@ -2688,7 +2604,7 @@
         <v>3</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O36" s="2">
         <v>37.1</v>
@@ -2699,7 +2615,7 @@
         <v>15</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O37" s="2">
         <v>40.549999999999997</v>
@@ -2707,13 +2623,13 @@
     </row>
     <row r="38" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M38" s="4" t="s">
         <v>1</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O38" s="3">
         <v>18.03</v>
@@ -2724,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>19</v>
@@ -2733,13 +2649,13 @@
         <v>20</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M39" s="4" t="s">
         <v>2</v>
       </c>
       <c r="N39" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O39" s="2">
         <v>23.67</v>
@@ -2759,22 +2675,22 @@
         <v>0.99619999999999997</v>
       </c>
       <c r="G40" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="J40" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="M40" s="4" t="s">
         <v>3</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O40" s="2">
         <v>24.01</v>
@@ -2794,7 +2710,7 @@
         <v>0.99780000000000002</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H41" s="3">
         <v>19.170000000000002</v>
@@ -2809,7 +2725,7 @@
         <v>15</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O41" s="2">
         <v>26.21</v>
@@ -2829,7 +2745,7 @@
         <v>0.99860000000000004</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H42" s="3">
         <v>18.510000000000002</v>
@@ -2871,8 +2787,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>